--- a/research/traditional_assets/database/data/chile/chile_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0372</v>
+        <v>0.03145</v>
       </c>
       <c r="E2">
-        <v>0.04626</v>
+        <v>0.483</v>
       </c>
       <c r="G2">
-        <v>0.5632708184690653</v>
+        <v>0.6058157256016106</v>
       </c>
       <c r="H2">
-        <v>0.5590323786226344</v>
+        <v>0.5886187886884043</v>
       </c>
       <c r="I2">
-        <v>0.4918469824349435</v>
+        <v>0.4128456438264196</v>
       </c>
       <c r="J2">
-        <v>0.4398588985131546</v>
+        <v>0.3668288973886727</v>
       </c>
       <c r="K2">
-        <v>1178.67</v>
+        <v>2539.93</v>
       </c>
       <c r="L2">
-        <v>1.001146672102742</v>
+        <v>2.389442886978118</v>
       </c>
       <c r="M2">
-        <v>643.3680000000001</v>
+        <v>1978.37</v>
       </c>
       <c r="N2">
-        <v>0.115396122181766</v>
+        <v>0.2061940446288055</v>
       </c>
       <c r="O2">
-        <v>0.5458423477309171</v>
+        <v>0.7789072927206656</v>
       </c>
       <c r="P2">
-        <v>632.668</v>
+        <v>1978.37</v>
       </c>
       <c r="Q2">
-        <v>0.1134769429447743</v>
+        <v>0.2061940446288055</v>
       </c>
       <c r="R2">
-        <v>0.5367643191054323</v>
+        <v>0.7789072927206656</v>
       </c>
       <c r="S2">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01663122816179853</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1230.965</v>
+        <v>852.838</v>
       </c>
       <c r="V2">
-        <v>0.2207890158377127</v>
+        <v>0.08888636434698322</v>
       </c>
       <c r="W2">
-        <v>0.1312564190345772</v>
+        <v>0.3175159594609483</v>
       </c>
       <c r="X2">
-        <v>0.05278697329515374</v>
+        <v>0.08297184863116824</v>
       </c>
       <c r="Y2">
-        <v>0.07846944573942345</v>
+        <v>0.2345441108297801</v>
       </c>
       <c r="Z2">
-        <v>0.1585935580106493</v>
+        <v>0.1355942894669705</v>
       </c>
       <c r="AA2">
-        <v>0.1070793192574939</v>
+        <v>0.136233656859871</v>
       </c>
       <c r="AB2">
-        <v>0.04894379241711518</v>
+        <v>0.08067206570509292</v>
       </c>
       <c r="AC2">
-        <v>0.05818442368660155</v>
+        <v>0.0554671606281717</v>
       </c>
       <c r="AD2">
-        <v>2935.08</v>
+        <v>1957.588</v>
       </c>
       <c r="AE2">
-        <v>1.548553198462249</v>
+        <v>0.7166876269621925</v>
       </c>
       <c r="AF2">
-        <v>2936.628553198462</v>
+        <v>1958.304687626962</v>
       </c>
       <c r="AG2">
-        <v>1705.663553198462</v>
+        <v>1105.466687626962</v>
       </c>
       <c r="AH2">
-        <v>0.3450015510403912</v>
+        <v>0.169506093053374</v>
       </c>
       <c r="AI2">
-        <v>0.2468827978532584</v>
+        <v>0.1696588197052401</v>
       </c>
       <c r="AJ2">
-        <v>0.2342634379002185</v>
+        <v>0.10331303426378</v>
       </c>
       <c r="AK2">
-        <v>0.1599479911468742</v>
+        <v>0.1034135467995295</v>
       </c>
       <c r="AL2">
-        <v>153.224</v>
+        <v>158.022</v>
       </c>
       <c r="AM2">
-        <v>109.058</v>
+        <v>101.228</v>
       </c>
       <c r="AN2">
-        <v>4.738562777384029</v>
+        <v>3.409719222462203</v>
       </c>
       <c r="AO2">
-        <v>3.778442019526967</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="AP2">
-        <v>2.753721814712654</v>
+        <v>1.92549760960594</v>
       </c>
       <c r="AQ2">
-        <v>5.308624768471822</v>
+        <v>4.336250839688624</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones PlanVital S.A. (SNSE:PLANVITAL)</t>
+          <t>Administradora Americana de Inversiones S.A. (SNSE:AAISA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,47 +721,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.357</v>
-      </c>
-      <c r="E3">
-        <v>0.975</v>
-      </c>
       <c r="G3">
-        <v>0.4520697167755992</v>
+        <v>0.4792780748663102</v>
       </c>
       <c r="H3">
-        <v>0.4520697167755992</v>
+        <v>0.4792780748663102</v>
       </c>
       <c r="I3">
-        <v>0.4411764705882353</v>
+        <v>0.4571969416751843</v>
       </c>
       <c r="J3">
-        <v>0.3327793033675386</v>
+        <v>0.2285984708375921</v>
       </c>
       <c r="K3">
-        <v>30.7</v>
+        <v>54.2</v>
       </c>
       <c r="L3">
-        <v>0.3344226579520697</v>
+        <v>0.3622994652406418</v>
       </c>
       <c r="M3">
-        <v>26.6</v>
+        <v>45</v>
       </c>
       <c r="N3">
-        <v>0.2252328535139712</v>
+        <v>0.2893890675241158</v>
       </c>
       <c r="O3">
-        <v>0.8664495114006515</v>
+        <v>0.8302583025830258</v>
       </c>
       <c r="P3">
-        <v>26.6</v>
+        <v>45</v>
       </c>
       <c r="Q3">
-        <v>0.2252328535139712</v>
+        <v>0.2893890675241158</v>
       </c>
       <c r="R3">
-        <v>0.8664495114006515</v>
+        <v>0.8302583025830258</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>54.2</v>
+        <v>71.2</v>
       </c>
       <c r="V3">
-        <v>0.4589331075359865</v>
-      </c>
-      <c r="W3">
-        <v>0.2940613026819923</v>
+        <v>0.4578778135048232</v>
       </c>
       <c r="X3">
-        <v>0.05001866091950151</v>
-      </c>
-      <c r="Y3">
-        <v>0.2440426417624908</v>
+        <v>0.08245513196013374</v>
       </c>
       <c r="Z3">
-        <v>1.298444130127298</v>
+        <v>208.73808109972</v>
       </c>
       <c r="AA3">
-        <v>0.432095333085432</v>
+        <v>47.71720614496928</v>
       </c>
       <c r="AB3">
-        <v>0.04875462377577432</v>
+        <v>0.08078384542411141</v>
       </c>
       <c r="AC3">
-        <v>0.3833407093096577</v>
+        <v>47.63642229954517</v>
       </c>
       <c r="AD3">
-        <v>5.46</v>
+        <v>7.86</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.7166876269621925</v>
       </c>
       <c r="AF3">
-        <v>5.46</v>
+        <v>8.576687626962192</v>
       </c>
       <c r="AG3">
-        <v>-48.74</v>
+        <v>-62.62331237303781</v>
       </c>
       <c r="AH3">
-        <v>0.04418905794755585</v>
+        <v>0.05227243279351047</v>
       </c>
       <c r="AI3">
-        <v>0.04881101376720901</v>
+        <v>0.0317918041859189</v>
       </c>
       <c r="AJ3">
-        <v>-0.7027104959630913</v>
+        <v>-0.6742629821658089</v>
       </c>
       <c r="AK3">
-        <v>-0.8453000346860908</v>
+        <v>-0.3153608468415957</v>
       </c>
       <c r="AL3">
-        <v>0.342</v>
+        <v>0.454</v>
       </c>
       <c r="AM3">
-        <v>0.276</v>
+        <v>-1.136</v>
       </c>
       <c r="AN3">
-        <v>0.1341523341523341</v>
+        <v>0.1107978573442346</v>
       </c>
       <c r="AO3">
-        <v>118.4210526315789</v>
+        <v>150.8810572687225</v>
       </c>
       <c r="AP3">
-        <v>-1.197542997542997</v>
+        <v>-0.8827644822813335</v>
       </c>
       <c r="AQ3">
-        <v>146.7391304347826</v>
+        <v>-60.29929577464788</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones Habitat S.A. (SNSE:HABITAT)</t>
+          <t>Administradora de Fondos de Pensiones PlanVital S.A. (SNSE:PLANVITAL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +844,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.112</v>
+        <v>0.348</v>
       </c>
       <c r="E4">
-        <v>0.0859</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="G4">
-        <v>0.6438986953184958</v>
+        <v>0.4163179916317992</v>
       </c>
       <c r="H4">
-        <v>0.6438986953184958</v>
+        <v>0.4163179916317992</v>
       </c>
       <c r="I4">
-        <v>0.5753729581998147</v>
+        <v>0.4675732217573222</v>
       </c>
       <c r="J4">
-        <v>0.4319692222189792</v>
+        <v>0.3659091530615036</v>
       </c>
       <c r="K4">
-        <v>171.9</v>
+        <v>35.9</v>
       </c>
       <c r="L4">
-        <v>0.4397544128933231</v>
+        <v>0.3755230125523012</v>
       </c>
       <c r="M4">
-        <v>123.5</v>
+        <v>34.4</v>
       </c>
       <c r="N4">
-        <v>0.2264393105977265</v>
+        <v>0.459279038718291</v>
       </c>
       <c r="O4">
-        <v>0.7184409540430483</v>
+        <v>0.958217270194986</v>
       </c>
       <c r="P4">
-        <v>123.5</v>
+        <v>34.4</v>
       </c>
       <c r="Q4">
-        <v>0.2264393105977265</v>
+        <v>0.459279038718291</v>
       </c>
       <c r="R4">
-        <v>0.7184409540430483</v>
+        <v>0.958217270194986</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>183.5</v>
+        <v>34.8</v>
       </c>
       <c r="V4">
-        <v>0.3364503116978365</v>
+        <v>0.4646194926568757</v>
       </c>
       <c r="W4">
-        <v>0.2747322998241969</v>
+        <v>0.3374060150375939</v>
       </c>
       <c r="X4">
-        <v>0.05495276833173145</v>
+        <v>0.08265916594185158</v>
       </c>
       <c r="Y4">
-        <v>0.2197795314924654</v>
+        <v>0.2547468490957424</v>
       </c>
       <c r="Z4">
-        <v>0.6349401748272903</v>
+        <v>1.657995143947277</v>
       </c>
       <c r="AA4">
-        <v>0.2742746134757273</v>
+        <v>0.6066755989018339</v>
       </c>
       <c r="AB4">
-        <v>0.04832390781100719</v>
+        <v>0.08029720505168211</v>
       </c>
       <c r="AC4">
-        <v>0.2259507056647201</v>
+        <v>0.5263783938501517</v>
       </c>
       <c r="AD4">
-        <v>132.8</v>
+        <v>4.63</v>
       </c>
       <c r="AE4">
-        <v>1.548553198462249</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>134.3485531984623</v>
+        <v>4.63</v>
       </c>
       <c r="AG4">
-        <v>-49.15144680153773</v>
+        <v>-30.17</v>
       </c>
       <c r="AH4">
-        <v>0.1976444856944584</v>
+        <v>0.05821702502200427</v>
       </c>
       <c r="AI4">
-        <v>0.1717027306770235</v>
+        <v>0.04806394684937195</v>
       </c>
       <c r="AJ4">
-        <v>-0.09904602539340973</v>
+        <v>-0.6744913928012518</v>
       </c>
       <c r="AK4">
-        <v>-0.08206288593413022</v>
+        <v>-0.49032992036405</v>
       </c>
       <c r="AL4">
-        <v>1</v>
+        <v>0.209</v>
       </c>
       <c r="AM4">
-        <v>-0.1100000000000001</v>
+        <v>-0.617</v>
       </c>
       <c r="AN4">
-        <v>0.5826529134839398</v>
+        <v>0.1022075055187638</v>
       </c>
       <c r="AO4">
-        <v>224.8</v>
+        <v>213.8755980861244</v>
       </c>
       <c r="AP4">
-        <v>-0.2156493500065273</v>
+        <v>-0.6660044150110376</v>
       </c>
       <c r="AQ4">
-        <v>-2043.636363636362</v>
+        <v>-72.44732576985413</v>
       </c>
     </row>
     <row r="5">
@@ -990,46 +978,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0372</v>
+        <v>0.0434</v>
       </c>
       <c r="E5">
-        <v>0.00662</v>
+        <v>0.0151</v>
       </c>
       <c r="G5">
-        <v>0.5557116104868914</v>
+        <v>0.5706126687435099</v>
       </c>
       <c r="H5">
-        <v>0.5557116104868914</v>
+        <v>0.5706126687435099</v>
       </c>
       <c r="I5">
-        <v>0.502808988764045</v>
+        <v>0.5264797507788163</v>
       </c>
       <c r="J5">
-        <v>0.376510996325683</v>
+        <v>0.4069720772891463</v>
       </c>
       <c r="K5">
-        <v>79</v>
+        <v>88.2</v>
       </c>
       <c r="L5">
-        <v>0.3698501872659176</v>
+        <v>0.4579439252336449</v>
       </c>
       <c r="M5">
-        <v>127.2</v>
+        <v>22.9</v>
       </c>
       <c r="N5">
-        <v>0.1381557510589769</v>
+        <v>0.02547558126599177</v>
       </c>
       <c r="O5">
-        <v>1.610126582278481</v>
+        <v>0.2596371882086168</v>
       </c>
       <c r="P5">
-        <v>127.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q5">
-        <v>0.1381557510589769</v>
+        <v>0.02547558126599177</v>
       </c>
       <c r="R5">
-        <v>1.610126582278481</v>
+        <v>0.2596371882086168</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>83.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="V5">
-        <v>0.09080047789725208</v>
+        <v>0.07041940149071087</v>
       </c>
       <c r="W5">
-        <v>0.1234760862769616</v>
+        <v>0.153819323334496</v>
       </c>
       <c r="X5">
-        <v>0.04901283190457718</v>
+        <v>0.08086564990792941</v>
       </c>
       <c r="Y5">
-        <v>0.07446325437238438</v>
+        <v>0.07295367342656658</v>
       </c>
       <c r="Z5">
-        <v>0.7087868330236262</v>
+        <v>0.7278636483881941</v>
       </c>
       <c r="AA5">
-        <v>0.266866036684251</v>
+        <v>0.2962201809678001</v>
       </c>
       <c r="AB5">
-        <v>0.04889374348452399</v>
+        <v>0.08076660083018768</v>
       </c>
       <c r="AC5">
-        <v>0.217972293199727</v>
+        <v>0.2154535801376125</v>
       </c>
       <c r="AD5">
-        <v>5.01</v>
+        <v>2.94</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5.01</v>
+        <v>2.94</v>
       </c>
       <c r="AG5">
-        <v>-78.58999999999999</v>
+        <v>-60.36</v>
       </c>
       <c r="AH5">
-        <v>0.005412062092880059</v>
+        <v>0.003260001774150625</v>
       </c>
       <c r="AI5">
-        <v>0.008661675973790217</v>
+        <v>0.005918589201594395</v>
       </c>
       <c r="AJ5">
-        <v>-0.09332510004631223</v>
+        <v>-0.07198225487156248</v>
       </c>
       <c r="AK5">
-        <v>-0.1588286412966593</v>
+        <v>-0.1392580287929125</v>
       </c>
       <c r="AL5">
-        <v>0.315</v>
+        <v>0.199</v>
       </c>
       <c r="AM5">
-        <v>0.25</v>
+        <v>-1.821</v>
       </c>
       <c r="AN5">
-        <v>0.04469223907225691</v>
+        <v>0.02789373814041746</v>
       </c>
       <c r="AO5">
-        <v>340.952380952381</v>
+        <v>509.5477386934674</v>
       </c>
       <c r="AP5">
-        <v>-0.7010704727921498</v>
+        <v>-0.5726755218216318</v>
       </c>
       <c r="AQ5">
-        <v>429.6</v>
+        <v>-55.6836902800659</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones ProVida S.A. (SNSE:PROVIDA)</t>
+          <t>Administradora de Fondos de Pensiones Habitat S.A. (SNSE:HABITAT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,46 +1112,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00663</v>
+        <v>0.00095</v>
       </c>
       <c r="E6">
-        <v>-0.0346</v>
+        <v>0.0184</v>
       </c>
       <c r="G6">
-        <v>0.5591517857142857</v>
+        <v>0.857008907641819</v>
       </c>
       <c r="H6">
-        <v>0.5591517857142857</v>
+        <v>0.7941865916549461</v>
       </c>
       <c r="I6">
-        <v>0.5256696428571429</v>
+        <v>0.6497890295358649</v>
       </c>
       <c r="J6">
-        <v>0.4198106527093596</v>
+        <v>0.6044721365951772</v>
       </c>
       <c r="K6">
-        <v>115.8</v>
+        <v>114</v>
       </c>
       <c r="L6">
-        <v>0.4308035714285714</v>
+        <v>0.5344585091420534</v>
       </c>
       <c r="M6">
-        <v>198.4</v>
+        <v>119.8</v>
       </c>
       <c r="N6">
-        <v>0.8456947996589941</v>
+        <v>0.210359964881475</v>
       </c>
       <c r="O6">
-        <v>1.713298791018998</v>
+        <v>1.050877192982456</v>
       </c>
       <c r="P6">
-        <v>198.4</v>
+        <v>119.8</v>
       </c>
       <c r="Q6">
-        <v>0.8456947996589941</v>
+        <v>0.210359964881475</v>
       </c>
       <c r="R6">
-        <v>1.713298791018998</v>
+        <v>1.050877192982456</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1172,73 +1160,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>110.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V6">
-        <v>0.4705882352941177</v>
+        <v>0.1424056189640035</v>
       </c>
       <c r="W6">
-        <v>0.07083002018472077</v>
+        <v>0.1759259259259259</v>
       </c>
       <c r="X6">
-        <v>0.04942101187210109</v>
+        <v>0.08682247994425349</v>
       </c>
       <c r="Y6">
-        <v>0.02140900831261969</v>
+        <v>0.08910344598167244</v>
       </c>
       <c r="Z6">
-        <v>0.3498815505167521</v>
+        <v>0.3605050112393733</v>
       </c>
       <c r="AA6">
-        <v>0.1468840020934004</v>
+        <v>0.2179152343971324</v>
       </c>
       <c r="AB6">
-        <v>0.04893866206845675</v>
+        <v>0.08036560764960218</v>
       </c>
       <c r="AC6">
-        <v>0.09794534002494368</v>
+        <v>0.1375496267475302</v>
       </c>
       <c r="AD6">
-        <v>5.16</v>
+        <v>112.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5.16</v>
+        <v>112.6</v>
       </c>
       <c r="AG6">
-        <v>-105.24</v>
+        <v>31.5</v>
       </c>
       <c r="AH6">
-        <v>0.02152152152152152</v>
+        <v>0.1650784342471778</v>
       </c>
       <c r="AI6">
-        <v>0.003426385826980796</v>
+        <v>0.2750366389838789</v>
       </c>
       <c r="AJ6">
-        <v>-0.8135435992578851</v>
+        <v>0.0524126455906822</v>
       </c>
       <c r="AK6">
-        <v>-0.07541058786436987</v>
+        <v>0.09594882729211088</v>
       </c>
       <c r="AL6">
-        <v>0.305</v>
+        <v>7.12</v>
       </c>
       <c r="AM6">
-        <v>0.305</v>
+        <v>2.75</v>
       </c>
       <c r="AN6">
-        <v>0.03426294820717132</v>
+        <v>0.8077474892395982</v>
       </c>
       <c r="AO6">
-        <v>463.2786885245902</v>
+        <v>19.46629213483146</v>
       </c>
       <c r="AP6">
-        <v>-0.6988047808764941</v>
+        <v>0.2259684361549498</v>
       </c>
       <c r="AQ6">
-        <v>463.2786885245902</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones Cuprum S.A. (SNSE:CUPRUM)</t>
+          <t>Administradora de Fondos de Pensiones ProVida S.A. (SNSE:PROVIDA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1258,46 +1246,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.00524</v>
+        <v>0.0194</v>
       </c>
       <c r="E7">
-        <v>-0.0489</v>
+        <v>0.0522</v>
       </c>
       <c r="G7">
-        <v>0.5763186813186814</v>
+        <v>0.5989435188947583</v>
       </c>
       <c r="H7">
-        <v>0.5489010989010989</v>
+        <v>0.5989435188947583</v>
       </c>
       <c r="I7">
-        <v>0.4230769230769231</v>
+        <v>0.5079236082893133</v>
       </c>
       <c r="J7">
-        <v>0.3467843631778058</v>
+        <v>0.4604742690860653</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>128.1</v>
       </c>
       <c r="L7">
-        <v>0.3571428571428572</v>
+        <v>0.5205201137748883</v>
       </c>
       <c r="M7">
-        <v>147.6</v>
+        <v>155.6</v>
       </c>
       <c r="N7">
-        <v>0.3269102990033222</v>
+        <v>0.3152350081037277</v>
       </c>
       <c r="O7">
-        <v>2.270769230769231</v>
+        <v>1.214676034348166</v>
       </c>
       <c r="P7">
-        <v>147.6</v>
+        <v>155.6</v>
       </c>
       <c r="Q7">
-        <v>0.3269102990033222</v>
+        <v>0.3152350081037277</v>
       </c>
       <c r="R7">
-        <v>2.270769230769231</v>
+        <v>1.214676034348166</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1306,73 +1294,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>78.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="V7">
-        <v>0.1738648947951273</v>
+        <v>0.1324959481361426</v>
       </c>
       <c r="W7">
-        <v>0.07247184747463485</v>
+        <v>0.0853544776119403</v>
       </c>
       <c r="X7">
-        <v>0.04946848871565819</v>
+        <v>0.08096778240701769</v>
       </c>
       <c r="Y7">
-        <v>0.02300335875897666</v>
+        <v>0.004386695204922617</v>
       </c>
       <c r="Z7">
-        <v>0.358832807570978</v>
+        <v>0.3564806767483632</v>
       </c>
       <c r="AA7">
-        <v>0.1244376066608057</v>
+        <v>0.1641501790690085</v>
       </c>
       <c r="AB7">
-        <v>0.04894379241711518</v>
+        <v>0.08076776232936102</v>
       </c>
       <c r="AC7">
-        <v>0.07549381424369055</v>
+        <v>0.08338241673964748</v>
       </c>
       <c r="AD7">
-        <v>10.8</v>
+        <v>3.26</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>10.8</v>
+        <v>3.26</v>
       </c>
       <c r="AG7">
-        <v>-67.7</v>
+        <v>-62.14000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.02336145360155743</v>
+        <v>0.006561204363402165</v>
       </c>
       <c r="AI7">
-        <v>0.01279772484891575</v>
+        <v>0.002682995078432341</v>
       </c>
       <c r="AJ7">
-        <v>-0.1763939551849922</v>
+        <v>-0.1440226208686785</v>
       </c>
       <c r="AK7">
-        <v>-0.0884504834073687</v>
+        <v>-0.05405076283422926</v>
       </c>
       <c r="AL7">
-        <v>0.345</v>
+        <v>0.486</v>
       </c>
       <c r="AM7">
-        <v>0.197</v>
+        <v>-0.126</v>
       </c>
       <c r="AN7">
-        <v>0.1167567567567568</v>
+        <v>0.02310418143160879</v>
       </c>
       <c r="AO7">
-        <v>223.1884057971015</v>
+        <v>257.201646090535</v>
       </c>
       <c r="AP7">
-        <v>-0.731891891891892</v>
+        <v>-0.440396881644224</v>
       </c>
       <c r="AQ7">
-        <v>390.8629441624366</v>
+        <v>-992.063492063492</v>
       </c>
     </row>
     <row r="8">
@@ -1392,46 +1380,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0668</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E8">
-        <v>-0.0726</v>
+        <v>0.0916</v>
       </c>
       <c r="G8">
-        <v>0.9912280701754387</v>
+        <v>0.8201058201058202</v>
       </c>
       <c r="H8">
-        <v>0.9912280701754387</v>
+        <v>0.8201058201058202</v>
       </c>
       <c r="I8">
-        <v>0.9327485380116959</v>
+        <v>0.9312169312169313</v>
       </c>
       <c r="J8">
-        <v>0.9327485380116959</v>
+        <v>0.9312169312169313</v>
       </c>
       <c r="K8">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="L8">
-        <v>0.9444444444444444</v>
+        <v>0.9338624338624338</v>
       </c>
       <c r="M8">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="N8">
-        <v>0.11796875</v>
+        <v>0.1178723404255319</v>
       </c>
       <c r="O8">
-        <v>0.934984520123839</v>
+        <v>0.7847025495750709</v>
       </c>
       <c r="P8">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="Q8">
-        <v>0.11796875</v>
+        <v>0.1178723404255319</v>
       </c>
       <c r="R8">
-        <v>0.934984520123839</v>
+        <v>0.7847025495750709</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1440,73 +1428,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="V8">
-        <v>0.0031640625</v>
+        <v>0.004595744680851064</v>
       </c>
       <c r="W8">
-        <v>0.1083892617449664</v>
+        <v>0.1389763779527559</v>
       </c>
       <c r="X8">
-        <v>0.04902313574713633</v>
+        <v>0.0807758826888768</v>
       </c>
       <c r="Y8">
-        <v>0.05936612599783011</v>
+        <v>0.05820049526387912</v>
       </c>
       <c r="Z8">
-        <v>0.1147997717431439</v>
+        <v>0.1484157210726766</v>
       </c>
       <c r="AA8">
-        <v>0.1070793192574939</v>
+        <v>0.1382072323216459</v>
       </c>
       <c r="AB8">
-        <v>0.04889489557089231</v>
+        <v>0.08076271666235735</v>
       </c>
       <c r="AC8">
-        <v>0.05818442368660155</v>
+        <v>0.0574445156592886</v>
       </c>
       <c r="AD8">
-        <v>0.15</v>
+        <v>0.008</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.15</v>
+        <v>0.008</v>
       </c>
       <c r="AG8">
-        <v>0.06899999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="AH8">
-        <v>0.005825242718446602</v>
+        <v>0.0003403096818104475</v>
       </c>
       <c r="AI8">
-        <v>0.005870841487279844</v>
+        <v>0.0004231013327691983</v>
       </c>
       <c r="AJ8">
-        <v>0.002688067318555456</v>
+        <v>-0.004273504273504274</v>
       </c>
       <c r="AK8">
-        <v>0.002709175860850445</v>
+        <v>-0.005319148936170214</v>
       </c>
       <c r="AL8">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AM8">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AN8">
-        <v>0.04702194357366771</v>
+        <v>0.002279202279202279</v>
       </c>
       <c r="AO8">
-        <v>1595</v>
+        <v>586.6666666666666</v>
       </c>
       <c r="AP8">
-        <v>0.02163009404388715</v>
+        <v>-0.02849002849002849</v>
       </c>
       <c r="AQ8">
-        <v>1595</v>
+        <v>586.6666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1505,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Betlan Dos S.A. (SNSE:BETLAN DOS)</t>
+          <t>Administradora de Fondos de Pensiones Cuprum S.A. (SNSE:CUPRUM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1526,112 +1514,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>2.353</v>
+        <v>0.0195</v>
       </c>
       <c r="E9">
-        <v>-0.391</v>
+        <v>0.011</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.5961728395061728</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.5660493827160494</v>
       </c>
       <c r="I9">
-        <v>0.02865671641791045</v>
+        <v>0.3907407407407407</v>
       </c>
       <c r="J9">
-        <v>0.02765750196386489</v>
+        <v>0.3644912580177943</v>
       </c>
       <c r="K9">
-        <v>2.94</v>
+        <v>66.8</v>
       </c>
       <c r="L9">
-        <v>0.1097014925373134</v>
+        <v>0.4123456790123456</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>61</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.1022460610124036</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.9131736526946108</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>61</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.1022460610124036</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.9131736526946108</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.484</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="V9">
-        <v>0.005046923879040667</v>
+        <v>0.1543747904793832</v>
       </c>
       <c r="W9">
-        <v>0.05686653771760154</v>
+        <v>0.08018245108630416</v>
       </c>
       <c r="X9">
-        <v>0.05278697329515374</v>
+        <v>0.08119113659103139</v>
       </c>
       <c r="Y9">
-        <v>0.004079564422447807</v>
+        <v>-0.001008685504727228</v>
       </c>
       <c r="Z9">
-        <v>0.4017087611481676</v>
+        <v>0.3683492496589359</v>
       </c>
       <c r="AA9">
-        <v>0.01111026085035718</v>
+        <v>0.1342600813980961</v>
       </c>
       <c r="AB9">
-        <v>0.04926013533587464</v>
+        <v>0.08077027580104133</v>
       </c>
       <c r="AC9">
-        <v>-0.03814987448551747</v>
+        <v>0.05348980559705481</v>
       </c>
       <c r="AD9">
-        <v>15.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>15.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AG9">
-        <v>14.716</v>
+        <v>-83.81</v>
       </c>
       <c r="AH9">
-        <v>0.1368136813681368</v>
+        <v>0.01370497115177966</v>
       </c>
       <c r="AI9">
-        <v>0.2222222222222222</v>
+        <v>0.01158808482086694</v>
       </c>
       <c r="AJ9">
-        <v>0.1330368120344254</v>
+        <v>-0.1634392246338657</v>
       </c>
       <c r="AK9">
-        <v>0.216679427528123</v>
+        <v>-0.1344638932118276</v>
       </c>
       <c r="AL9">
-        <v>0.315</v>
+        <v>0.248</v>
       </c>
       <c r="AM9">
-        <v>-1.775</v>
+        <v>-3.782</v>
+      </c>
+      <c r="AN9">
+        <v>0.1093667546174142</v>
       </c>
       <c r="AO9">
-        <v>2.438095238095238</v>
+        <v>255.2419354838709</v>
+      </c>
+      <c r="AP9">
+        <v>-1.105672823218997</v>
       </c>
       <c r="AQ9">
-        <v>-0.4326760563380282</v>
+        <v>-16.73717609730301</v>
       </c>
     </row>
     <row r="10">
@@ -1642,7 +1639,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sociedad de Inversiones Pampa Calichera S.A. (SNSE:CALICHERAA)</t>
+          <t>Nitratos de Chile S.A. (SNSE:NITRATOS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1651,28 +1648,28 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.447</v>
+        <v>0.757</v>
       </c>
       <c r="K10">
-        <v>226.8</v>
+        <v>237.9</v>
       </c>
       <c r="M10">
-        <v>4.25</v>
+        <v>38.2</v>
       </c>
       <c r="N10">
-        <v>0.004022335794056408</v>
+        <v>0.06712352837814092</v>
       </c>
       <c r="O10">
-        <v>0.0187389770723104</v>
+        <v>0.1605716687683901</v>
       </c>
       <c r="P10">
-        <v>4.25</v>
+        <v>38.2</v>
       </c>
       <c r="Q10">
-        <v>0.004022335794056408</v>
+        <v>0.06712352837814092</v>
       </c>
       <c r="R10">
-        <v>0.0187389770723104</v>
+        <v>0.1605716687683901</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1681,67 +1678,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>221.3</v>
+        <v>9.27</v>
       </c>
       <c r="V10">
-        <v>0.209445390876396</v>
+        <v>0.01628887717448603</v>
       </c>
       <c r="W10">
-        <v>0.1721442125237192</v>
+        <v>0.929296875</v>
       </c>
       <c r="X10">
-        <v>0.06459880180829068</v>
+        <v>0.09953605343558944</v>
       </c>
       <c r="Y10">
-        <v>0.1075454107154285</v>
+        <v>0.8297608215644106</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>-0.001368560483228264</v>
+        <v>-0.00161961367013373</v>
       </c>
       <c r="AB10">
-        <v>0.04996420540784882</v>
+        <v>0.07984520239574831</v>
       </c>
       <c r="AC10">
-        <v>-0.05133276589107708</v>
+        <v>-0.08146481606588205</v>
       </c>
       <c r="AD10">
-        <v>673.6</v>
+        <v>348.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>673.6</v>
+        <v>348.7</v>
       </c>
       <c r="AG10">
-        <v>452.3</v>
+        <v>339.43</v>
       </c>
       <c r="AH10">
-        <v>0.3893191538550457</v>
+        <v>0.3799302680322511</v>
       </c>
       <c r="AI10">
-        <v>0.3198480531813865</v>
+        <v>0.4444869343530911</v>
       </c>
       <c r="AJ10">
-        <v>0.2997547882563457</v>
+        <v>0.3736035133677479</v>
       </c>
       <c r="AK10">
-        <v>0.2399851435241683</v>
+        <v>0.4378442526734002</v>
       </c>
       <c r="AL10">
-        <v>37.8</v>
+        <v>16.7</v>
       </c>
       <c r="AM10">
-        <v>15.3</v>
+        <v>16.344</v>
       </c>
       <c r="AO10">
-        <v>-0.06587301587301589</v>
+        <v>-0.06526946107784432</v>
       </c>
       <c r="AQ10">
-        <v>-0.1627450980392157</v>
+        <v>-0.06669114047968674</v>
       </c>
     </row>
     <row r="11">
@@ -1752,7 +1749,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sociedad de Inversiones Oro Blanco S.A. (SNSE:ORO BLANCO)</t>
+          <t>Sociedad de Inversiones Pampa Calichera S.A. (SNSE:CALICHERAA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1761,97 +1758,97 @@
         </is>
       </c>
       <c r="E11">
-        <v>0.5579999999999999</v>
+        <v>0.483</v>
       </c>
       <c r="K11">
-        <v>191.7</v>
+        <v>568.8</v>
       </c>
       <c r="M11">
-        <v>12.43</v>
+        <v>498.3</v>
       </c>
       <c r="N11">
-        <v>0.01317993850068922</v>
+        <v>0.2499247667770087</v>
       </c>
       <c r="O11">
-        <v>0.06484089723526343</v>
+        <v>0.8760548523206751</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>498.3</v>
       </c>
       <c r="Q11">
-        <v>0.001834375994062135</v>
+        <v>0.2499247667770087</v>
       </c>
       <c r="R11">
-        <v>0.009024517475221702</v>
+        <v>0.8760548523206751</v>
       </c>
       <c r="S11">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.8608205953338697</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>224</v>
+        <v>135.5</v>
       </c>
       <c r="V11">
-        <v>0.2375145795779875</v>
+        <v>0.06796067810211656</v>
       </c>
       <c r="W11">
-        <v>0.1312564190345772</v>
+        <v>0.3970957833007539</v>
       </c>
       <c r="X11">
-        <v>0.06817711246149383</v>
+        <v>0.08743848297547398</v>
       </c>
       <c r="Y11">
-        <v>0.06307930657308336</v>
+        <v>0.3096573003252799</v>
       </c>
       <c r="Z11">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>-0.002302398868094412</v>
+        <v>-0.005327696435098657</v>
       </c>
       <c r="AB11">
-        <v>0.04912636707340291</v>
+        <v>0.08082838560318995</v>
       </c>
       <c r="AC11">
-        <v>-0.05142876594149733</v>
+        <v>-0.0861560820382886</v>
       </c>
       <c r="AD11">
-        <v>738.1</v>
+        <v>434.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>738.1</v>
+        <v>434.3</v>
       </c>
       <c r="AG11">
-        <v>514.1</v>
+        <v>298.8</v>
       </c>
       <c r="AH11">
-        <v>0.439031644063764</v>
+        <v>0.1788641324492402</v>
       </c>
       <c r="AI11">
-        <v>0.2999187322226737</v>
+        <v>0.2134466997591783</v>
       </c>
       <c r="AJ11">
-        <v>0.3527998902003843</v>
+        <v>0.130332373724156</v>
       </c>
       <c r="AK11">
-        <v>0.229816718819848</v>
+        <v>0.157329401853412</v>
       </c>
       <c r="AL11">
-        <v>42.1</v>
+        <v>34.9</v>
       </c>
       <c r="AM11">
-        <v>24.7</v>
+        <v>12.3</v>
       </c>
       <c r="AO11">
-        <v>-0.0850356294536817</v>
+        <v>-0.2951289398280803</v>
       </c>
       <c r="AQ11">
-        <v>-0.1449392712550607</v>
+        <v>-0.8373983739837401</v>
       </c>
     </row>
     <row r="12">
@@ -1862,7 +1859,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nitratos de Chile S.A. (SNSE:NITRATOS)</t>
+          <t>Norte Grande S.A. (SNSE:NORTEGRAN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1870,26 +1867,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E12">
+        <v>0.618</v>
+      </c>
       <c r="K12">
-        <v>83.90000000000001</v>
+        <v>532.2</v>
       </c>
       <c r="M12">
-        <v>0.005</v>
+        <v>467.6</v>
       </c>
       <c r="N12">
-        <v>2.115059221658206e-05</v>
+        <v>0.2482085036360741</v>
       </c>
       <c r="O12">
-        <v>5.959475566150178e-05</v>
+        <v>0.8786170612551673</v>
       </c>
       <c r="P12">
-        <v>0.005</v>
+        <v>467.6</v>
       </c>
       <c r="Q12">
-        <v>2.115059221658206e-05</v>
+        <v>0.2482085036360741</v>
       </c>
       <c r="R12">
-        <v>5.959475566150178e-05</v>
+        <v>0.8786170612551673</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1898,67 +1898,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>25.4</v>
+        <v>154.6</v>
       </c>
       <c r="V12">
-        <v>0.1074450084602369</v>
+        <v>0.08206380381124263</v>
       </c>
       <c r="W12">
-        <v>0.4207622868605818</v>
+        <v>0.3881271878646441</v>
       </c>
       <c r="X12">
-        <v>0.09502452208960531</v>
+        <v>0.08916932609885654</v>
       </c>
       <c r="Y12">
-        <v>0.3257377647709764</v>
+        <v>0.2989578617657876</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>-0.003949886897511745</v>
+        <v>-0.006066905216499847</v>
       </c>
       <c r="AB12">
-        <v>0.04924638229955679</v>
+        <v>0.08024403438562186</v>
       </c>
       <c r="AC12">
-        <v>-0.05319626919706853</v>
+        <v>-0.0863109396021217</v>
       </c>
       <c r="AD12">
-        <v>442.4</v>
+        <v>516.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>442.4</v>
+        <v>516.8</v>
       </c>
       <c r="AG12">
-        <v>417</v>
+        <v>362.1999999999999</v>
       </c>
       <c r="AH12">
-        <v>0.6517383618149676</v>
+        <v>0.2152705460907235</v>
       </c>
       <c r="AI12">
-        <v>0.6304688613367535</v>
+        <v>0.1983877159309021</v>
       </c>
       <c r="AJ12">
-        <v>0.6382001836547291</v>
+        <v>0.1612572904144962</v>
       </c>
       <c r="AK12">
-        <v>0.616590270589975</v>
+        <v>0.1478126020241593</v>
       </c>
       <c r="AL12">
-        <v>19.8</v>
+        <v>45.1</v>
       </c>
       <c r="AM12">
-        <v>19.702</v>
+        <v>42.62</v>
+      </c>
+      <c r="AN12">
+        <v>-70.50477489768076</v>
       </c>
       <c r="AO12">
-        <v>-0.1146464646464646</v>
+        <v>-0.1636363636363636</v>
+      </c>
+      <c r="AP12">
+        <v>-49.41336971350613</v>
       </c>
       <c r="AQ12">
-        <v>-0.1152167292660644</v>
+        <v>-0.1731581417175035</v>
       </c>
     </row>
     <row r="13">
@@ -1969,7 +1975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Norte Grande S.A. (SNSE:NORTEGRAN)</t>
+          <t>Sociedad de Inversiones Oro Blanco S.A. (SNSE:ORO BLANCO)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,28 +1984,28 @@
         </is>
       </c>
       <c r="E13">
-        <v>0.8440000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="K13">
-        <v>207.7</v>
+        <v>465.1</v>
       </c>
       <c r="M13">
-        <v>0.363</v>
+        <v>489.1</v>
       </c>
       <c r="N13">
-        <v>0.000383153894870171</v>
+        <v>0.2913564067433133</v>
       </c>
       <c r="O13">
-        <v>0.001747713047664901</v>
+        <v>1.051601806063212</v>
       </c>
       <c r="P13">
-        <v>0.363</v>
+        <v>489.1</v>
       </c>
       <c r="Q13">
-        <v>0.000383153894870171</v>
+        <v>0.2913564067433133</v>
       </c>
       <c r="R13">
-        <v>0.001747713047664901</v>
+        <v>1.051601806063212</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2008,73 +2014,177 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>249.5</v>
+        <v>140.5</v>
       </c>
       <c r="V13">
-        <v>0.2633523327000211</v>
+        <v>0.08369571692381009</v>
       </c>
       <c r="W13">
-        <v>0.1656960510570403</v>
+        <v>0.2976259038843028</v>
       </c>
       <c r="X13">
-        <v>0.07246994350707553</v>
+        <v>0.08923669078230023</v>
       </c>
       <c r="Y13">
-        <v>0.09322610754996474</v>
+        <v>0.2083892131020026</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>-0.006880157875852172</v>
+        <v>-0.009999843959310261</v>
       </c>
       <c r="AB13">
-        <v>0.04915452771976639</v>
+        <v>0.0802407601401469</v>
       </c>
       <c r="AC13">
-        <v>-0.05603468559561856</v>
+        <v>-0.09024060409945717</v>
       </c>
       <c r="AD13">
-        <v>906.4</v>
+        <v>464.2</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>906.4</v>
+        <v>464.2</v>
       </c>
       <c r="AG13">
-        <v>656.9</v>
+        <v>323.7</v>
       </c>
       <c r="AH13">
-        <v>0.4889416334016615</v>
+        <v>0.2166223342199823</v>
       </c>
       <c r="AI13">
-        <v>0.3345143194567464</v>
+        <v>0.1998364113823238</v>
       </c>
       <c r="AJ13">
-        <v>0.409462070685034</v>
+        <v>0.1616560127846584</v>
       </c>
       <c r="AK13">
-        <v>0.2670216657859437</v>
+        <v>0.1483229472140762</v>
       </c>
       <c r="AL13">
-        <v>50.9</v>
+        <v>37.9</v>
       </c>
       <c r="AM13">
-        <v>50.211</v>
-      </c>
-      <c r="AN13">
-        <v>-119.1064388961892</v>
+        <v>21.1</v>
       </c>
       <c r="AO13">
-        <v>-0.1506876227897839</v>
-      </c>
-      <c r="AP13">
-        <v>-86.32063074901444</v>
+        <v>-0.4538258575197889</v>
       </c>
       <c r="AQ13">
-        <v>-0.1527553723287726</v>
+        <v>-0.8151658767772513</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Potasios de Chile S.A. (SNSE:POTASIOS-A)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>0.679</v>
+      </c>
+      <c r="K14">
+        <v>245.2</v>
+      </c>
+      <c r="M14">
+        <v>43.7</v>
+      </c>
+      <c r="N14">
+        <v>0.0665448454393178</v>
+      </c>
+      <c r="O14">
+        <v>0.1782218597063622</v>
+      </c>
+      <c r="P14">
+        <v>43.7</v>
+      </c>
+      <c r="Q14">
+        <v>0.0665448454393178</v>
+      </c>
+      <c r="R14">
+        <v>0.1782218597063622</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>4.96</v>
+      </c>
+      <c r="V14">
+        <v>0.007552916095629663</v>
+      </c>
+      <c r="W14">
+        <v>0.7211764705882353</v>
+      </c>
+      <c r="X14">
+        <v>0.08328453132048493</v>
+      </c>
+      <c r="Y14">
+        <v>0.6378919392677503</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>-0.1451345755693582</v>
+      </c>
+      <c r="AB14">
+        <v>0.0805814147478285</v>
+      </c>
+      <c r="AC14">
+        <v>-0.2257159903171866</v>
+      </c>
+      <c r="AD14">
+        <v>54</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>54</v>
+      </c>
+      <c r="AG14">
+        <v>49.04</v>
+      </c>
+      <c r="AH14">
+        <v>0.07598142676234698</v>
+      </c>
+      <c r="AI14">
+        <v>0.09409304756926294</v>
+      </c>
+      <c r="AJ14">
+        <v>0.06948734661490066</v>
+      </c>
+      <c r="AK14">
+        <v>0.08619538088374873</v>
+      </c>
+      <c r="AL14">
+        <v>14.7</v>
+      </c>
+      <c r="AM14">
+        <v>13.59</v>
+      </c>
+      <c r="AO14">
+        <v>-4.768707482993197</v>
+      </c>
+      <c r="AQ14">
+        <v>-5.158204562178072</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03145</v>
+        <v>0.0597</v>
       </c>
       <c r="E2">
-        <v>0.483</v>
+        <v>0.491</v>
       </c>
       <c r="G2">
-        <v>0.6058157256016106</v>
+        <v>0.5192214778071249</v>
       </c>
       <c r="H2">
-        <v>0.5886187886884043</v>
+        <v>0.5107904399922696</v>
       </c>
       <c r="I2">
-        <v>0.4128456438264196</v>
+        <v>0.5263995361721318</v>
       </c>
       <c r="J2">
-        <v>0.3668288973886727</v>
+        <v>0.4697645675634264</v>
       </c>
       <c r="K2">
-        <v>2539.93</v>
+        <v>2750.76</v>
       </c>
       <c r="L2">
-        <v>2.389442886978118</v>
+        <v>2.215067963666817</v>
       </c>
       <c r="M2">
-        <v>1978.37</v>
+        <v>1804.52</v>
       </c>
       <c r="N2">
-        <v>0.2061940446288055</v>
+        <v>0.165596351322829</v>
       </c>
       <c r="O2">
-        <v>0.7789072927206656</v>
+        <v>0.6560077942096003</v>
       </c>
       <c r="P2">
-        <v>1978.37</v>
+        <v>1804.52</v>
       </c>
       <c r="Q2">
-        <v>0.2061940446288055</v>
+        <v>0.165596351322829</v>
       </c>
       <c r="R2">
-        <v>0.7789072927206656</v>
+        <v>0.6560077942096003</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>852.838</v>
+        <v>946.773</v>
       </c>
       <c r="V2">
-        <v>0.08888636434698322</v>
+        <v>0.08688302392379624</v>
       </c>
       <c r="W2">
-        <v>0.3175159594609483</v>
+        <v>0.317989417989418</v>
       </c>
       <c r="X2">
-        <v>0.08297184863116824</v>
+        <v>0.06894430493847786</v>
       </c>
       <c r="Y2">
-        <v>0.2345441108297801</v>
+        <v>0.2490451130509401</v>
       </c>
       <c r="Z2">
-        <v>0.1355942894669705</v>
+        <v>0.1629285362671596</v>
       </c>
       <c r="AA2">
-        <v>0.136233656859871</v>
+        <v>0.1418319332582777</v>
       </c>
       <c r="AB2">
-        <v>0.08067206570509292</v>
+        <v>0.06859656274055288</v>
       </c>
       <c r="AC2">
-        <v>0.0554671606281717</v>
+        <v>0.07323537051772484</v>
       </c>
       <c r="AD2">
-        <v>1957.588</v>
+        <v>1356.755</v>
       </c>
       <c r="AE2">
-        <v>0.7166876269621925</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1958.304687626962</v>
+        <v>1356.755</v>
       </c>
       <c r="AG2">
-        <v>1105.466687626962</v>
+        <v>409.9820000000001</v>
       </c>
       <c r="AH2">
-        <v>0.169506093053374</v>
+        <v>0.1107206670880307</v>
       </c>
       <c r="AI2">
-        <v>0.1696588197052401</v>
+        <v>0.1135905922973011</v>
       </c>
       <c r="AJ2">
-        <v>0.10331303426378</v>
+        <v>0.03625886855689205</v>
       </c>
       <c r="AK2">
-        <v>0.1034135467995295</v>
+        <v>0.03727962455405702</v>
       </c>
       <c r="AL2">
-        <v>158.022</v>
+        <v>102.348</v>
       </c>
       <c r="AM2">
-        <v>101.228</v>
+        <v>35.22499999999999</v>
       </c>
       <c r="AN2">
-        <v>3.409719222462203</v>
+        <v>1.971970291561292</v>
       </c>
       <c r="AO2">
-        <v>2.777777777777778</v>
+        <v>6.38707155977645</v>
       </c>
       <c r="AP2">
-        <v>1.92549760960594</v>
+        <v>0.5958867474782711</v>
       </c>
       <c r="AQ2">
-        <v>4.336250839688624</v>
+        <v>18.55795599716111</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Administradora Americana de Inversiones S.A. (SNSE:AAISA)</t>
+          <t>Administradora de Fondos de Pensiones PlanVital S.A. (SNSE:PLANVITAL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,41 +721,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.311</v>
+      </c>
+      <c r="E3">
+        <v>0.5770000000000001</v>
+      </c>
       <c r="G3">
-        <v>0.4792780748663102</v>
+        <v>0.451559934318555</v>
       </c>
       <c r="H3">
-        <v>0.4792780748663102</v>
+        <v>0.451559934318555</v>
       </c>
       <c r="I3">
-        <v>0.4571969416751843</v>
+        <v>0.4967159277504105</v>
       </c>
       <c r="J3">
-        <v>0.2285984708375921</v>
+        <v>0.3725369458128079</v>
       </c>
       <c r="K3">
-        <v>54.2</v>
+        <v>47.4</v>
       </c>
       <c r="L3">
-        <v>0.3622994652406418</v>
+        <v>0.3891625615763547</v>
       </c>
       <c r="M3">
-        <v>45</v>
+        <v>31.5</v>
       </c>
       <c r="N3">
-        <v>0.2893890675241158</v>
+        <v>0.1053511705685619</v>
       </c>
       <c r="O3">
-        <v>0.8302583025830258</v>
+        <v>0.6645569620253164</v>
       </c>
       <c r="P3">
-        <v>45</v>
+        <v>31.5</v>
       </c>
       <c r="Q3">
-        <v>0.2893890675241158</v>
+        <v>0.1053511705685619</v>
       </c>
       <c r="R3">
-        <v>0.8302583025830258</v>
+        <v>0.6645569620253164</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>71.2</v>
+        <v>45.4</v>
       </c>
       <c r="V3">
-        <v>0.4578778135048232</v>
+        <v>0.1518394648829431</v>
+      </c>
+      <c r="W3">
+        <v>0.5169029443838604</v>
       </c>
       <c r="X3">
-        <v>0.08245513196013374</v>
+        <v>0.06894430493847786</v>
+      </c>
+      <c r="Y3">
+        <v>0.4479586394453826</v>
       </c>
       <c r="Z3">
-        <v>208.73808109972</v>
+        <v>1.979522184300341</v>
       </c>
       <c r="AA3">
-        <v>47.71720614496928</v>
+        <v>0.7374451487079473</v>
       </c>
       <c r="AB3">
-        <v>0.08078384542411141</v>
+        <v>0.0685910393930997</v>
       </c>
       <c r="AC3">
-        <v>47.63642229954517</v>
+        <v>0.6688541093148476</v>
       </c>
       <c r="AD3">
-        <v>7.86</v>
+        <v>4.27</v>
       </c>
       <c r="AE3">
-        <v>0.7166876269621925</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.576687626962192</v>
+        <v>4.27</v>
       </c>
       <c r="AG3">
-        <v>-62.62331237303781</v>
+        <v>-41.13</v>
       </c>
       <c r="AH3">
-        <v>0.05227243279351047</v>
+        <v>0.01407986282850265</v>
       </c>
       <c r="AI3">
-        <v>0.0317918041859189</v>
+        <v>0.03586125808348031</v>
       </c>
       <c r="AJ3">
-        <v>-0.6742629821658089</v>
+        <v>-0.1594989723504091</v>
       </c>
       <c r="AK3">
-        <v>-0.3153608468415957</v>
+        <v>-0.5583005293878104</v>
       </c>
       <c r="AL3">
-        <v>0.454</v>
+        <v>0.205</v>
       </c>
       <c r="AM3">
-        <v>-1.136</v>
+        <v>-1.935</v>
       </c>
       <c r="AN3">
-        <v>0.1107978573442346</v>
+        <v>0.06988543371522093</v>
       </c>
       <c r="AO3">
-        <v>150.8810572687225</v>
+        <v>295.1219512195122</v>
       </c>
       <c r="AP3">
-        <v>-0.8827644822813335</v>
+        <v>-0.6731587561374794</v>
       </c>
       <c r="AQ3">
-        <v>-60.29929577464788</v>
+        <v>-31.26614987080103</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones PlanVital S.A. (SNSE:PLANVITAL)</t>
+          <t>Administradora de Fondos de Pensiones Capital S.A. (SNSE:AFPCAPITAL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.348</v>
+        <v>0.0762</v>
       </c>
       <c r="E4">
-        <v>0.7240000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="G4">
-        <v>0.4163179916317992</v>
+        <v>0.5395744680851063</v>
       </c>
       <c r="H4">
-        <v>0.4163179916317992</v>
+        <v>0.5395744680851063</v>
       </c>
       <c r="I4">
-        <v>0.4675732217573222</v>
+        <v>0.5685106382978723</v>
       </c>
       <c r="J4">
-        <v>0.3659091530615036</v>
+        <v>0.4276407456222934</v>
       </c>
       <c r="K4">
-        <v>35.9</v>
+        <v>110.5</v>
       </c>
       <c r="L4">
-        <v>0.3755230125523012</v>
+        <v>0.4702127659574468</v>
       </c>
       <c r="M4">
-        <v>34.4</v>
+        <v>29.7</v>
       </c>
       <c r="N4">
-        <v>0.459279038718291</v>
+        <v>0.0333295926383122</v>
       </c>
       <c r="O4">
-        <v>0.958217270194986</v>
+        <v>0.2687782805429864</v>
       </c>
       <c r="P4">
-        <v>34.4</v>
+        <v>29.7</v>
       </c>
       <c r="Q4">
-        <v>0.459279038718291</v>
+        <v>0.0333295926383122</v>
       </c>
       <c r="R4">
-        <v>0.958217270194986</v>
+        <v>0.2687782805429864</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>34.8</v>
+        <v>115.2</v>
       </c>
       <c r="V4">
-        <v>0.4646194926568757</v>
+        <v>0.1292784199304231</v>
       </c>
       <c r="W4">
-        <v>0.3374060150375939</v>
+        <v>0.2237748076144188</v>
       </c>
       <c r="X4">
-        <v>0.08265916594185158</v>
+        <v>0.06867190526899471</v>
       </c>
       <c r="Y4">
-        <v>0.2547468490957424</v>
+        <v>0.1551029023454241</v>
       </c>
       <c r="Z4">
-        <v>1.657995143947277</v>
+        <v>0.9818668003676778</v>
       </c>
       <c r="AA4">
-        <v>0.6066755989018339</v>
+        <v>0.4198862506110091</v>
       </c>
       <c r="AB4">
-        <v>0.08029720505168211</v>
+        <v>0.06863142762364001</v>
       </c>
       <c r="AC4">
-        <v>0.5263783938501517</v>
+        <v>0.3512548229873692</v>
       </c>
       <c r="AD4">
-        <v>4.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG4">
-        <v>-30.17</v>
+        <v>-113.62</v>
       </c>
       <c r="AH4">
-        <v>0.05821702502200427</v>
+        <v>0.001769951158309809</v>
       </c>
       <c r="AI4">
-        <v>0.04806394684937195</v>
+        <v>0.002835199540625897</v>
       </c>
       <c r="AJ4">
-        <v>-0.6744913928012518</v>
+        <v>-0.14613880742913</v>
       </c>
       <c r="AK4">
-        <v>-0.49032992036405</v>
+        <v>-0.2570123054650742</v>
       </c>
       <c r="AL4">
-        <v>0.209</v>
+        <v>0.128</v>
       </c>
       <c r="AM4">
-        <v>-0.617</v>
+        <v>-5.141999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.1022075055187638</v>
+        <v>0.01146589259796807</v>
       </c>
       <c r="AO4">
-        <v>213.8755980861244</v>
+        <v>1043.75</v>
       </c>
       <c r="AP4">
-        <v>-0.6660044150110376</v>
+        <v>-0.8245283018867924</v>
       </c>
       <c r="AQ4">
-        <v>-72.44732576985413</v>
+        <v>-25.98210812913263</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones Capital S.A. (SNSE:AFPCAPITAL)</t>
+          <t>Administradora de Fondos de Pensiones Habitat S.A. (SNSE:HABITAT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0434</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="E5">
-        <v>0.0151</v>
+        <v>0.0476</v>
       </c>
       <c r="G5">
-        <v>0.5706126687435099</v>
+        <v>0.620954356846473</v>
       </c>
       <c r="H5">
-        <v>0.5706126687435099</v>
+        <v>0.6002766251728907</v>
       </c>
       <c r="I5">
-        <v>0.5264797507788163</v>
+        <v>0.634508990318119</v>
       </c>
       <c r="J5">
-        <v>0.4069720772891463</v>
+        <v>0.4694876018919268</v>
       </c>
       <c r="K5">
-        <v>88.2</v>
+        <v>134</v>
       </c>
       <c r="L5">
-        <v>0.4579439252336449</v>
+        <v>0.4633471645919779</v>
       </c>
       <c r="M5">
-        <v>22.9</v>
+        <v>120.9</v>
       </c>
       <c r="N5">
-        <v>0.02547558126599177</v>
+        <v>0.1284393923297567</v>
       </c>
       <c r="O5">
-        <v>0.2596371882086168</v>
+        <v>0.9022388059701493</v>
       </c>
       <c r="P5">
-        <v>22.9</v>
+        <v>120.9</v>
       </c>
       <c r="Q5">
-        <v>0.02547558126599177</v>
+        <v>0.1284393923297567</v>
       </c>
       <c r="R5">
-        <v>0.2596371882086168</v>
+        <v>0.9022388059701493</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>63.3</v>
+        <v>82.8</v>
       </c>
       <c r="V5">
-        <v>0.07041940149071087</v>
+        <v>0.08796345479655795</v>
       </c>
       <c r="W5">
-        <v>0.153819323334496</v>
+        <v>0.4514824797843666</v>
       </c>
       <c r="X5">
-        <v>0.08086564990792941</v>
+        <v>0.07138189580543877</v>
       </c>
       <c r="Y5">
-        <v>0.07295367342656658</v>
+        <v>0.3801005839789278</v>
       </c>
       <c r="Z5">
-        <v>0.7278636483881941</v>
+        <v>0.8809016143770942</v>
       </c>
       <c r="AA5">
-        <v>0.2962201809678001</v>
+        <v>0.4135723864366288</v>
       </c>
       <c r="AB5">
-        <v>0.08076660083018768</v>
+        <v>0.06782154040401683</v>
       </c>
       <c r="AC5">
-        <v>0.2154535801376125</v>
+        <v>0.345750846032612</v>
       </c>
       <c r="AD5">
-        <v>2.94</v>
+        <v>118.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.94</v>
+        <v>118.8</v>
       </c>
       <c r="AG5">
-        <v>-60.36</v>
+        <v>36</v>
       </c>
       <c r="AH5">
-        <v>0.003260001774150625</v>
+        <v>0.1120648995377795</v>
       </c>
       <c r="AI5">
-        <v>0.005918589201594395</v>
+        <v>0.2655935613682092</v>
       </c>
       <c r="AJ5">
-        <v>-0.07198225487156248</v>
+        <v>0.03683618131587026</v>
       </c>
       <c r="AK5">
-        <v>-0.1392580287929125</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="AL5">
-        <v>0.199</v>
+        <v>12.9</v>
       </c>
       <c r="AM5">
-        <v>-1.821</v>
+        <v>5.630000000000001</v>
       </c>
       <c r="AN5">
-        <v>0.02789373814041746</v>
+        <v>0.6520307354555434</v>
       </c>
       <c r="AO5">
-        <v>509.5477386934674</v>
+        <v>14.22480620155039</v>
       </c>
       <c r="AP5">
-        <v>-0.5726755218216318</v>
+        <v>0.1975850713501647</v>
       </c>
       <c r="AQ5">
-        <v>-55.6836902800659</v>
+        <v>32.59325044404973</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones Habitat S.A. (SNSE:HABITAT)</t>
+          <t>Inversiones Tricahue S.A. (SNSE:TRICAHUE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,46 +1124,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00095</v>
+        <v>0.187</v>
       </c>
       <c r="E6">
-        <v>0.0184</v>
+        <v>0.201</v>
       </c>
       <c r="G6">
-        <v>0.857008907641819</v>
+        <v>0.8102893890675241</v>
       </c>
       <c r="H6">
-        <v>0.7941865916549461</v>
+        <v>0.8102893890675241</v>
       </c>
       <c r="I6">
-        <v>0.6497890295358649</v>
+        <v>0.9501607717041801</v>
       </c>
       <c r="J6">
-        <v>0.6044721365951772</v>
+        <v>0.9501607717041801</v>
       </c>
       <c r="K6">
-        <v>114</v>
+        <v>6.01</v>
       </c>
       <c r="L6">
-        <v>0.5344585091420534</v>
+        <v>0.9662379421221865</v>
       </c>
       <c r="M6">
-        <v>119.8</v>
+        <v>5.72</v>
       </c>
       <c r="N6">
-        <v>0.210359964881475</v>
+        <v>0.1687315634218289</v>
       </c>
       <c r="O6">
-        <v>1.050877192982456</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P6">
-        <v>119.8</v>
+        <v>5.72</v>
       </c>
       <c r="Q6">
-        <v>0.210359964881475</v>
+        <v>0.1687315634218289</v>
       </c>
       <c r="R6">
-        <v>1.050877192982456</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,73 +1172,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>81.09999999999999</v>
+        <v>0.257</v>
       </c>
       <c r="V6">
-        <v>0.1424056189640035</v>
+        <v>0.007581120943952802</v>
       </c>
       <c r="W6">
-        <v>0.1759259259259259</v>
+        <v>0.317989417989418</v>
       </c>
       <c r="X6">
-        <v>0.08682247994425349</v>
+        <v>0.06863650253065787</v>
       </c>
       <c r="Y6">
-        <v>0.08910344598167244</v>
+        <v>0.2493529154587601</v>
       </c>
       <c r="Z6">
-        <v>0.3605050112393733</v>
+        <v>0.3308510638297873</v>
       </c>
       <c r="AA6">
-        <v>0.2179152343971324</v>
+        <v>0.3143617021276596</v>
       </c>
       <c r="AB6">
-        <v>0.08036560764960218</v>
+        <v>0.06863222217606241</v>
       </c>
       <c r="AC6">
-        <v>0.1375496267475302</v>
+        <v>0.2457294799515972</v>
       </c>
       <c r="AD6">
-        <v>112.6</v>
+        <v>0.005</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>112.6</v>
+        <v>0.005</v>
       </c>
       <c r="AG6">
-        <v>31.5</v>
+        <v>-0.252</v>
       </c>
       <c r="AH6">
-        <v>0.1650784342471778</v>
+        <v>0.0001474708745022858</v>
       </c>
       <c r="AI6">
-        <v>0.2750366389838789</v>
+        <v>0.0001243626414625047</v>
       </c>
       <c r="AJ6">
-        <v>0.0524126455906822</v>
+        <v>-0.007489300998573468</v>
       </c>
       <c r="AK6">
-        <v>0.09594882729211088</v>
+        <v>-0.006308200660859116</v>
       </c>
       <c r="AL6">
-        <v>7.12</v>
+        <v>0.001</v>
       </c>
       <c r="AM6">
-        <v>2.75</v>
+        <v>0.001</v>
       </c>
       <c r="AN6">
-        <v>0.8077474892395982</v>
+        <v>0.0008460236886632825</v>
       </c>
       <c r="AO6">
-        <v>19.46629213483146</v>
+        <v>5910</v>
       </c>
       <c r="AP6">
-        <v>0.2259684361549498</v>
+        <v>-0.04263959390862944</v>
       </c>
       <c r="AQ6">
-        <v>50.4</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones ProVida S.A. (SNSE:PROVIDA)</t>
+          <t>Administradora de Fondos de Pensiones Provida S.A. (SNSE:PROVIDA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,46 +1258,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0194</v>
+        <v>0.0597</v>
       </c>
       <c r="E7">
-        <v>0.0522</v>
+        <v>0.104</v>
       </c>
       <c r="G7">
-        <v>0.5989435188947583</v>
+        <v>0.5559265442404007</v>
       </c>
       <c r="H7">
-        <v>0.5989435188947583</v>
+        <v>0.5559265442404007</v>
       </c>
       <c r="I7">
-        <v>0.5079236082893133</v>
+        <v>0.5252086811352255</v>
       </c>
       <c r="J7">
-        <v>0.4604742690860653</v>
+        <v>0.4155428589588637</v>
       </c>
       <c r="K7">
-        <v>128.1</v>
+        <v>133</v>
       </c>
       <c r="L7">
-        <v>0.5205201137748883</v>
+        <v>0.4440734557595993</v>
       </c>
       <c r="M7">
-        <v>155.6</v>
+        <v>123</v>
       </c>
       <c r="N7">
-        <v>0.3152350081037277</v>
+        <v>0.1226198783770312</v>
       </c>
       <c r="O7">
-        <v>1.214676034348166</v>
+        <v>0.924812030075188</v>
       </c>
       <c r="P7">
-        <v>155.6</v>
+        <v>123</v>
       </c>
       <c r="Q7">
-        <v>0.3152350081037277</v>
+        <v>0.1226198783770312</v>
       </c>
       <c r="R7">
-        <v>1.214676034348166</v>
+        <v>0.924812030075188</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1294,73 +1306,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>65.40000000000001</v>
+        <v>130.8</v>
       </c>
       <c r="V7">
-        <v>0.1324959481361426</v>
+        <v>0.1303957731033795</v>
       </c>
       <c r="W7">
-        <v>0.0853544776119403</v>
+        <v>0.1097540848324806</v>
       </c>
       <c r="X7">
-        <v>0.08096778240701769</v>
+        <v>0.06869451540577871</v>
       </c>
       <c r="Y7">
-        <v>0.004386695204922617</v>
+        <v>0.0410595694267019</v>
       </c>
       <c r="Z7">
-        <v>0.3564806767483632</v>
+        <v>0.5392898300201672</v>
       </c>
       <c r="AA7">
-        <v>0.1641501790690085</v>
+        <v>0.2240980377740198</v>
       </c>
       <c r="AB7">
-        <v>0.08076776232936102</v>
+        <v>0.06862487790833244</v>
       </c>
       <c r="AC7">
-        <v>0.08338241673964748</v>
+        <v>0.1554731598656874</v>
       </c>
       <c r="AD7">
-        <v>3.26</v>
+        <v>2.82</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.26</v>
+        <v>2.82</v>
       </c>
       <c r="AG7">
-        <v>-62.14000000000001</v>
+        <v>-127.98</v>
       </c>
       <c r="AH7">
-        <v>0.006561204363402165</v>
+        <v>0.002803403849212661</v>
       </c>
       <c r="AI7">
-        <v>0.002682995078432341</v>
+        <v>0.002140872443479449</v>
       </c>
       <c r="AJ7">
-        <v>-0.1440226208686785</v>
+        <v>-0.1462428009872932</v>
       </c>
       <c r="AK7">
-        <v>-0.05405076283422926</v>
+        <v>-0.1078707371757051</v>
       </c>
       <c r="AL7">
-        <v>0.486</v>
+        <v>0.449</v>
       </c>
       <c r="AM7">
-        <v>-0.126</v>
+        <v>-1.471</v>
       </c>
       <c r="AN7">
-        <v>0.02310418143160879</v>
+        <v>0.01656874265569918</v>
       </c>
       <c r="AO7">
-        <v>257.201646090535</v>
+        <v>350.3340757238308</v>
       </c>
       <c r="AP7">
-        <v>-0.440396881644224</v>
+        <v>-0.7519388954171564</v>
       </c>
       <c r="AQ7">
-        <v>-992.063492063492</v>
+        <v>-106.9340584636302</v>
       </c>
     </row>
     <row r="8">
@@ -1371,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inversiones Tricahue S.A. (SNSE:TRICAHUE)</t>
+          <t>Administradora de Fondos de Pensiones Cuprum S.A. (SNSE:CUPRUM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1380,46 +1392,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.09810000000000001</v>
+        <v>0.0548</v>
       </c>
       <c r="E8">
-        <v>0.0916</v>
+        <v>0.0679</v>
       </c>
       <c r="G8">
-        <v>0.8201058201058202</v>
+        <v>0.5215512753774076</v>
       </c>
       <c r="H8">
-        <v>0.8201058201058202</v>
+        <v>0.4981780322748569</v>
       </c>
       <c r="I8">
-        <v>0.9312169312169313</v>
+        <v>0.4575741801145237</v>
       </c>
       <c r="J8">
-        <v>0.9312169312169313</v>
+        <v>0.3614648492503051</v>
       </c>
       <c r="K8">
-        <v>3.53</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="L8">
-        <v>0.9338624338624338</v>
+        <v>0.4013534617386778</v>
       </c>
       <c r="M8">
-        <v>2.77</v>
+        <v>41.7</v>
       </c>
       <c r="N8">
-        <v>0.1178723404255319</v>
+        <v>0.05327711766960521</v>
       </c>
       <c r="O8">
-        <v>0.7847025495750709</v>
+        <v>0.5408560311284047</v>
       </c>
       <c r="P8">
-        <v>2.77</v>
+        <v>41.7</v>
       </c>
       <c r="Q8">
-        <v>0.1178723404255319</v>
+        <v>0.05327711766960521</v>
       </c>
       <c r="R8">
-        <v>0.7847025495750709</v>
+        <v>0.5408560311284047</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1428,73 +1440,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.108</v>
+        <v>81</v>
       </c>
       <c r="V8">
-        <v>0.004595744680851064</v>
+        <v>0.1034879264085857</v>
       </c>
       <c r="W8">
-        <v>0.1389763779527559</v>
+        <v>0.1090369113279593</v>
       </c>
       <c r="X8">
-        <v>0.0807758826888768</v>
+        <v>0.06882472353042558</v>
       </c>
       <c r="Y8">
-        <v>0.05820049526387912</v>
+        <v>0.04021218779753367</v>
       </c>
       <c r="Z8">
-        <v>0.1484157210726766</v>
+        <v>0.5509191545498868</v>
       </c>
       <c r="AA8">
-        <v>0.1382072323216459</v>
+        <v>0.1991379091484804</v>
       </c>
       <c r="AB8">
-        <v>0.08076271666235735</v>
+        <v>0.06862411995951487</v>
       </c>
       <c r="AC8">
-        <v>0.0574445156592886</v>
+        <v>0.1305137891889655</v>
       </c>
       <c r="AD8">
-        <v>0.008</v>
+        <v>6.88</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.008</v>
+        <v>6.88</v>
       </c>
       <c r="AG8">
-        <v>-0.1</v>
+        <v>-74.12</v>
       </c>
       <c r="AH8">
-        <v>0.0003403096818104475</v>
+        <v>0.008713493249575724</v>
       </c>
       <c r="AI8">
-        <v>0.0004231013327691983</v>
+        <v>0.009510907130415549</v>
       </c>
       <c r="AJ8">
-        <v>-0.004273504273504274</v>
+        <v>-0.1046035733438708</v>
       </c>
       <c r="AK8">
-        <v>-0.005319148936170214</v>
+        <v>-0.11538341791463</v>
       </c>
       <c r="AL8">
-        <v>0.006</v>
+        <v>0.525</v>
       </c>
       <c r="AM8">
-        <v>0.006</v>
+        <v>-6.955</v>
       </c>
       <c r="AN8">
-        <v>0.002279202279202279</v>
+        <v>0.07020408163265306</v>
       </c>
       <c r="AO8">
-        <v>586.6666666666666</v>
+        <v>167.4285714285714</v>
       </c>
       <c r="AP8">
-        <v>-0.02849002849002849</v>
+        <v>-0.756326530612245</v>
       </c>
       <c r="AQ8">
-        <v>586.6666666666666</v>
+        <v>-12.63838964773544</v>
       </c>
     </row>
     <row r="9">
@@ -1505,7 +1517,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Administradora de Fondos de Pensiones Cuprum S.A. (SNSE:CUPRUM)</t>
+          <t>Administradora Americana de Inversiones S.A. (SNSE:AAISA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1513,47 +1525,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0195</v>
-      </c>
-      <c r="E9">
-        <v>0.011</v>
-      </c>
       <c r="G9">
-        <v>0.5961728395061728</v>
+        <v>0.1971399387129724</v>
       </c>
       <c r="H9">
-        <v>0.5660493827160494</v>
+        <v>0.1971399387129724</v>
       </c>
       <c r="I9">
-        <v>0.3907407407407407</v>
+        <v>0.3534218590398366</v>
       </c>
       <c r="J9">
-        <v>0.3644912580177943</v>
+        <v>0.2788105776869822</v>
       </c>
       <c r="K9">
-        <v>66.8</v>
+        <v>33.3</v>
       </c>
       <c r="L9">
-        <v>0.4123456790123456</v>
+        <v>0.3401430030643514</v>
       </c>
       <c r="M9">
-        <v>61</v>
+        <v>11.2</v>
       </c>
       <c r="N9">
-        <v>0.1022460610124036</v>
+        <v>0.05132905591200733</v>
       </c>
       <c r="O9">
-        <v>0.9131736526946108</v>
+        <v>0.3363363363363364</v>
       </c>
       <c r="P9">
-        <v>61</v>
+        <v>11.2</v>
       </c>
       <c r="Q9">
-        <v>0.1022460610124036</v>
+        <v>0.05132905591200733</v>
       </c>
       <c r="R9">
-        <v>0.9131736526946108</v>
+        <v>0.3363363363363364</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1562,73 +1568,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>92.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="V9">
-        <v>0.1543747904793832</v>
+        <v>0.3363886342804767</v>
       </c>
       <c r="W9">
-        <v>0.08018245108630416</v>
+        <v>0.1275373420145538</v>
       </c>
       <c r="X9">
-        <v>0.08119113659103139</v>
+        <v>0.0694207826129373</v>
       </c>
       <c r="Y9">
-        <v>-0.001008685504727228</v>
+        <v>0.0581165594016165</v>
       </c>
       <c r="Z9">
-        <v>0.3683492496589359</v>
+        <v>0.508703559366069</v>
       </c>
       <c r="AA9">
-        <v>0.1342600813980961</v>
+        <v>0.1418319332582777</v>
       </c>
       <c r="AB9">
-        <v>0.08077027580104133</v>
+        <v>0.06859656274055288</v>
       </c>
       <c r="AC9">
-        <v>0.05348980559705481</v>
+        <v>0.07323537051772484</v>
       </c>
       <c r="AD9">
-        <v>8.289999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>8.289999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="AG9">
-        <v>-83.81</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.01370497115177966</v>
+        <v>0.03489760714759609</v>
       </c>
       <c r="AI9">
-        <v>0.01158808482086694</v>
+        <v>0.02497704897274368</v>
       </c>
       <c r="AJ9">
-        <v>-0.1634392246338657</v>
+        <v>-0.4290392298120375</v>
       </c>
       <c r="AK9">
-        <v>-0.1344638932118276</v>
+        <v>-0.2701554703286734</v>
       </c>
       <c r="AL9">
-        <v>0.248</v>
+        <v>0.264</v>
       </c>
       <c r="AM9">
-        <v>-3.782</v>
+        <v>-1.676</v>
       </c>
       <c r="AN9">
-        <v>0.1093667546174142</v>
+        <v>0.2191666666666666</v>
       </c>
       <c r="AO9">
-        <v>255.2419354838709</v>
+        <v>131.0606060606061</v>
       </c>
       <c r="AP9">
-        <v>-1.105672823218997</v>
+        <v>-1.819722222222222</v>
       </c>
       <c r="AQ9">
-        <v>-16.73717609730301</v>
+        <v>-20.64439140811456</v>
       </c>
     </row>
     <row r="10">
@@ -1639,7 +1645,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nitratos de Chile S.A. (SNSE:NITRATOS)</t>
+          <t>Sociedad de Inversiones Pampa Calichera S.A. (SNSE:CALICHERAA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1648,28 +1654,28 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.757</v>
+        <v>0.491</v>
       </c>
       <c r="K10">
-        <v>237.9</v>
+        <v>587.5</v>
       </c>
       <c r="M10">
-        <v>38.2</v>
+        <v>379.5</v>
       </c>
       <c r="N10">
-        <v>0.06712352837814092</v>
+        <v>0.1920449369971155</v>
       </c>
       <c r="O10">
-        <v>0.1605716687683901</v>
+        <v>0.6459574468085106</v>
       </c>
       <c r="P10">
-        <v>38.2</v>
+        <v>379.5</v>
       </c>
       <c r="Q10">
-        <v>0.06712352837814092</v>
+        <v>0.1920449369971155</v>
       </c>
       <c r="R10">
-        <v>0.1605716687683901</v>
+        <v>0.6459574468085106</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1678,67 +1684,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>9.27</v>
+        <v>118.5</v>
       </c>
       <c r="V10">
-        <v>0.01628887717448603</v>
+        <v>0.05996660088052224</v>
       </c>
       <c r="W10">
-        <v>0.929296875</v>
+        <v>0.3670957260684828</v>
       </c>
       <c r="X10">
-        <v>0.09953605343558944</v>
+        <v>0.06863450268523864</v>
       </c>
       <c r="Y10">
-        <v>0.8297608215644106</v>
+        <v>0.2984612233832442</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>-0.00161961367013373</v>
+        <v>0.0003321956439740745</v>
       </c>
       <c r="AB10">
-        <v>0.07984520239574831</v>
+        <v>0.06863323181067911</v>
       </c>
       <c r="AC10">
-        <v>-0.08146481606588205</v>
+        <v>-0.06830103616670503</v>
       </c>
       <c r="AD10">
-        <v>348.7</v>
+        <v>0.11</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>348.7</v>
+        <v>0.11</v>
       </c>
       <c r="AG10">
-        <v>339.43</v>
+        <v>-118.39</v>
       </c>
       <c r="AH10">
-        <v>0.3799302680322511</v>
+        <v>5.566210068767996e-05</v>
       </c>
       <c r="AI10">
-        <v>0.4444869343530911</v>
+        <v>6.408351830167025e-05</v>
       </c>
       <c r="AJ10">
-        <v>0.3736035133677479</v>
+        <v>-0.06372899968240468</v>
       </c>
       <c r="AK10">
-        <v>0.4378442526734002</v>
+        <v>-0.07408589433107428</v>
       </c>
       <c r="AL10">
-        <v>16.7</v>
+        <v>25.1</v>
       </c>
       <c r="AM10">
-        <v>16.344</v>
+        <v>17.78</v>
       </c>
       <c r="AO10">
-        <v>-0.06526946107784432</v>
+        <v>0.02521912350597609</v>
       </c>
       <c r="AQ10">
-        <v>-0.06669114047968674</v>
+        <v>0.03560179977502812</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sociedad de Inversiones Pampa Calichera S.A. (SNSE:CALICHERAA)</t>
+          <t>Sociedad de Inversiones Oro Blanco S.A. (SNSE:ORO BLANCO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1758,28 +1764,28 @@
         </is>
       </c>
       <c r="E11">
-        <v>0.483</v>
+        <v>0.54</v>
       </c>
       <c r="K11">
-        <v>568.8</v>
+        <v>514.3</v>
       </c>
       <c r="M11">
-        <v>498.3</v>
+        <v>377.4</v>
       </c>
       <c r="N11">
-        <v>0.2499247667770087</v>
+        <v>0.2192019515595051</v>
       </c>
       <c r="O11">
-        <v>0.8760548523206751</v>
+        <v>0.7338129496402878</v>
       </c>
       <c r="P11">
-        <v>498.3</v>
+        <v>377.4</v>
       </c>
       <c r="Q11">
-        <v>0.2499247667770087</v>
+        <v>0.2192019515595051</v>
       </c>
       <c r="R11">
-        <v>0.8760548523206751</v>
+        <v>0.7338129496402878</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1788,67 +1794,67 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>135.5</v>
+        <v>122.1</v>
       </c>
       <c r="V11">
-        <v>0.06796067810211656</v>
+        <v>0.07091827844572225</v>
       </c>
       <c r="W11">
-        <v>0.3970957833007539</v>
+        <v>0.3061674008810573</v>
       </c>
       <c r="X11">
-        <v>0.08743848297547398</v>
+        <v>0.07399659412759094</v>
       </c>
       <c r="Y11">
-        <v>0.3096573003252799</v>
+        <v>0.2321708067534663</v>
       </c>
       <c r="Z11">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>-0.005327696435098657</v>
+        <v>-0.001899660482443065</v>
       </c>
       <c r="AB11">
-        <v>0.08082838560318995</v>
+        <v>0.06804031672156564</v>
       </c>
       <c r="AC11">
-        <v>-0.0861560820382886</v>
+        <v>-0.06993997720400871</v>
       </c>
       <c r="AD11">
-        <v>434.3</v>
+        <v>424</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>434.3</v>
+        <v>424</v>
       </c>
       <c r="AG11">
-        <v>298.8</v>
+        <v>301.9</v>
       </c>
       <c r="AH11">
-        <v>0.1788641324492402</v>
+        <v>0.197604511348278</v>
       </c>
       <c r="AI11">
-        <v>0.2134466997591783</v>
+        <v>0.1769911504424779</v>
       </c>
       <c r="AJ11">
-        <v>0.130332373724156</v>
+        <v>0.1491895631547737</v>
       </c>
       <c r="AK11">
-        <v>0.157329401853412</v>
+        <v>0.1327908511106224</v>
       </c>
       <c r="AL11">
-        <v>34.9</v>
+        <v>26.1</v>
       </c>
       <c r="AM11">
-        <v>12.3</v>
+        <v>-2.699999999999999</v>
       </c>
       <c r="AO11">
-        <v>-0.2951289398280803</v>
+        <v>-0.110727969348659</v>
       </c>
       <c r="AQ11">
-        <v>-0.8373983739837401</v>
+        <v>1.070370370370371</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1865,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Norte Grande S.A. (SNSE:NORTEGRAN)</t>
+          <t>Nitratos de Chile S.A. (SNSE:NITRATOS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1868,28 +1874,28 @@
         </is>
       </c>
       <c r="E12">
-        <v>0.618</v>
+        <v>0.675</v>
       </c>
       <c r="K12">
-        <v>532.2</v>
+        <v>243.3</v>
       </c>
       <c r="M12">
-        <v>467.6</v>
+        <v>155.9</v>
       </c>
       <c r="N12">
-        <v>0.2482085036360741</v>
+        <v>0.2908039544861034</v>
       </c>
       <c r="O12">
-        <v>0.8786170612551673</v>
+        <v>0.6407727085902178</v>
       </c>
       <c r="P12">
-        <v>467.6</v>
+        <v>155.9</v>
       </c>
       <c r="Q12">
-        <v>0.2482085036360741</v>
+        <v>0.2908039544861034</v>
       </c>
       <c r="R12">
-        <v>0.8786170612551673</v>
+        <v>0.6407727085902178</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1898,73 +1904,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>154.6</v>
+        <v>20.1</v>
       </c>
       <c r="V12">
-        <v>0.08206380381124263</v>
+        <v>0.03749300503637381</v>
       </c>
       <c r="W12">
-        <v>0.3881271878646441</v>
+        <v>0.5647632311977716</v>
       </c>
       <c r="X12">
-        <v>0.08916932609885654</v>
+        <v>0.08141346909864609</v>
       </c>
       <c r="Y12">
-        <v>0.2989578617657876</v>
+        <v>0.4833497620991255</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>-0.006066905216499847</v>
+        <v>-0.002999104163691365</v>
       </c>
       <c r="AB12">
-        <v>0.08024403438562186</v>
+        <v>0.06752355141473218</v>
       </c>
       <c r="AC12">
-        <v>-0.0863109396021217</v>
+        <v>-0.07052265557842355</v>
       </c>
       <c r="AD12">
-        <v>516.8</v>
+        <v>314.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>516.8</v>
+        <v>314.6</v>
       </c>
       <c r="AG12">
-        <v>362.1999999999999</v>
+        <v>294.5</v>
       </c>
       <c r="AH12">
-        <v>0.2152705460907235</v>
+        <v>0.3698130950981545</v>
       </c>
       <c r="AI12">
-        <v>0.1983877159309021</v>
+        <v>0.3668376865671642</v>
       </c>
       <c r="AJ12">
-        <v>0.1612572904144962</v>
+        <v>0.3545629665302191</v>
       </c>
       <c r="AK12">
-        <v>0.1478126020241593</v>
+        <v>0.3516417910447761</v>
       </c>
       <c r="AL12">
-        <v>45.1</v>
+        <v>15.3</v>
       </c>
       <c r="AM12">
-        <v>42.62</v>
-      </c>
-      <c r="AN12">
-        <v>-70.50477489768076</v>
+        <v>14.635</v>
       </c>
       <c r="AO12">
-        <v>-0.1636363636363636</v>
-      </c>
-      <c r="AP12">
-        <v>-49.41336971350613</v>
+        <v>-0.1509803921568627</v>
       </c>
       <c r="AQ12">
-        <v>-0.1731581417175035</v>
+        <v>-0.1578407926204305</v>
       </c>
     </row>
     <row r="13">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sociedad de Inversiones Oro Blanco S.A. (SNSE:ORO BLANCO)</t>
+          <t>Norte Grande S.A. (SNSE:NORTEGRAN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1984,28 +1984,28 @@
         </is>
       </c>
       <c r="E13">
-        <v>0.514</v>
+        <v>0.632</v>
       </c>
       <c r="K13">
-        <v>465.1</v>
+        <v>616.3</v>
       </c>
       <c r="M13">
-        <v>489.1</v>
+        <v>370.5</v>
       </c>
       <c r="N13">
-        <v>0.2913564067433133</v>
+        <v>0.2044701986754967</v>
       </c>
       <c r="O13">
-        <v>1.051601806063212</v>
+        <v>0.6011682622099628</v>
       </c>
       <c r="P13">
-        <v>489.1</v>
+        <v>370.5</v>
       </c>
       <c r="Q13">
-        <v>0.2913564067433133</v>
+        <v>0.2044701986754967</v>
       </c>
       <c r="R13">
-        <v>1.051601806063212</v>
+        <v>0.6011682622099628</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2014,67 +2014,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>140.5</v>
+        <v>142.5</v>
       </c>
       <c r="V13">
-        <v>0.08369571692381009</v>
+        <v>0.07864238410596026</v>
       </c>
       <c r="W13">
-        <v>0.2976259038843028</v>
+        <v>0.3874638501194518</v>
       </c>
       <c r="X13">
-        <v>0.08923669078230023</v>
+        <v>0.07403339584552458</v>
       </c>
       <c r="Y13">
-        <v>0.2083892131020026</v>
+        <v>0.3134304542739272</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>-0.009999843959310261</v>
+        <v>-0.003028320403776055</v>
       </c>
       <c r="AB13">
-        <v>0.0802407601401469</v>
+        <v>0.0680370563197972</v>
       </c>
       <c r="AC13">
-        <v>-0.09024060409945717</v>
+        <v>-0.07106537672357326</v>
       </c>
       <c r="AD13">
-        <v>464.2</v>
+        <v>449.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>464.2</v>
+        <v>449.3</v>
       </c>
       <c r="AG13">
-        <v>323.7</v>
+        <v>306.8</v>
       </c>
       <c r="AH13">
-        <v>0.2166223342199823</v>
+        <v>0.1986910184407199</v>
       </c>
       <c r="AI13">
-        <v>0.1998364113823238</v>
+        <v>0.1632156349898285</v>
       </c>
       <c r="AJ13">
-        <v>0.1616560127846584</v>
+        <v>0.1447989427978101</v>
       </c>
       <c r="AK13">
-        <v>0.1483229472140762</v>
+        <v>0.1175343830211087</v>
       </c>
       <c r="AL13">
-        <v>37.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AM13">
-        <v>21.1</v>
+        <v>6.749999999999999</v>
+      </c>
+      <c r="AN13">
+        <v>-140.846394984326</v>
       </c>
       <c r="AO13">
-        <v>-0.4538258575197889</v>
+        <v>-0.390832328106152</v>
+      </c>
+      <c r="AP13">
+        <v>-96.1755485893417</v>
       </c>
       <c r="AQ13">
-        <v>-0.8151658767772513</v>
+        <v>-0.4800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2094,28 +2100,28 @@
         </is>
       </c>
       <c r="E14">
-        <v>0.679</v>
+        <v>0.602</v>
       </c>
       <c r="K14">
-        <v>245.2</v>
+        <v>247</v>
       </c>
       <c r="M14">
-        <v>43.7</v>
+        <v>157.5</v>
       </c>
       <c r="N14">
-        <v>0.0665448454393178</v>
+        <v>0.2672209026128266</v>
       </c>
       <c r="O14">
-        <v>0.1782218597063622</v>
+        <v>0.6376518218623481</v>
       </c>
       <c r="P14">
-        <v>43.7</v>
+        <v>157.5</v>
       </c>
       <c r="Q14">
-        <v>0.0665448454393178</v>
+        <v>0.2672209026128266</v>
       </c>
       <c r="R14">
-        <v>0.1782218597063622</v>
+        <v>0.6376518218623481</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2124,67 +2130,189 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>4.96</v>
+        <v>14.7</v>
       </c>
       <c r="V14">
-        <v>0.007552916095629663</v>
+        <v>0.02494061757719715</v>
       </c>
       <c r="W14">
-        <v>0.7211764705882353</v>
+        <v>0.4750913637237931</v>
       </c>
       <c r="X14">
-        <v>0.08328453132048493</v>
+        <v>0.06961246413218314</v>
       </c>
       <c r="Y14">
-        <v>0.6378919392677503</v>
+        <v>0.4054788995916099</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>-0.1451345755693582</v>
+        <v>-0.002618905332724013</v>
       </c>
       <c r="AB14">
-        <v>0.0805814147478285</v>
+        <v>0.06850417612763131</v>
       </c>
       <c r="AC14">
-        <v>-0.2257159903171866</v>
+        <v>-0.07112308146035533</v>
       </c>
       <c r="AD14">
-        <v>54</v>
+        <v>26.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>54</v>
+        <v>26.5</v>
       </c>
       <c r="AG14">
-        <v>49.04</v>
+        <v>11.8</v>
       </c>
       <c r="AH14">
-        <v>0.07598142676234698</v>
+        <v>0.04302646533528171</v>
       </c>
       <c r="AI14">
-        <v>0.09409304756926294</v>
+        <v>0.04075042288174689</v>
       </c>
       <c r="AJ14">
-        <v>0.06948734661490066</v>
+        <v>0.01962741184298071</v>
       </c>
       <c r="AK14">
-        <v>0.08619538088374873</v>
+        <v>0.01856513530522342</v>
       </c>
       <c r="AL14">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="AM14">
-        <v>13.59</v>
+        <v>12.062</v>
       </c>
       <c r="AO14">
-        <v>-4.768707482993197</v>
+        <v>-0.11640625</v>
       </c>
       <c r="AQ14">
-        <v>-5.158204562178072</v>
+        <v>-0.123528436411872</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Betlan Dos S.A. (SNSE:BETLAN DOS)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.318</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>-2.575</v>
+      </c>
+      <c r="J15">
+        <v>-2.572547619047619</v>
+      </c>
+      <c r="K15">
+        <v>1.05</v>
+      </c>
+      <c r="L15">
+        <v>8.75</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0.016</v>
+      </c>
+      <c r="V15">
+        <v>0.000172972972972973</v>
+      </c>
+      <c r="W15">
+        <v>0.02258064516129032</v>
+      </c>
+      <c r="X15">
+        <v>0.06863329039172189</v>
+      </c>
+      <c r="Y15">
+        <v>-0.04605264523043157</v>
+      </c>
+      <c r="Z15">
+        <v>0.002022858298776171</v>
+      </c>
+      <c r="AA15">
+        <v>-0.005203899300187356</v>
+      </c>
+      <c r="AB15">
+        <v>0.06863329039172189</v>
+      </c>
+      <c r="AC15">
+        <v>-0.07383718969190925</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>-0.016</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.0001730028977985381</v>
+      </c>
+      <c r="AK15">
+        <v>-0.0003132096155351969</v>
+      </c>
+      <c r="AL15">
+        <v>0.286</v>
+      </c>
+      <c r="AM15">
+        <v>-1.754</v>
+      </c>
+      <c r="AO15">
+        <v>-1.08041958041958</v>
+      </c>
+      <c r="AQ15">
+        <v>0.1761687571265678</v>
       </c>
     </row>
   </sheetData>
